--- a/Шпаргалка.xlsx
+++ b/Шпаргалка.xlsx
@@ -1,16 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\TOP\html\top_py\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" activeTab="4"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Общие операции" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Строки" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Циклы" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Списки" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Словари" sheetId="5" r:id="rId8"/>
+    <sheet name="Общие операции" sheetId="1" r:id="rId1"/>
+    <sheet name="Строки" sheetId="2" r:id="rId2"/>
+    <sheet name="Циклы" sheetId="3" r:id="rId3"/>
+    <sheet name="Списки" sheetId="4" r:id="rId4"/>
+    <sheet name="Словари" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -553,16 +561,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
       </rPr>
       <t>range(4)</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve"> - это просто последовательность</t>
     </r>
@@ -573,16 +583,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">i </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">- название перменной, в которой хранится 
 каждое значение последовательности. Оно может быть любым. </t>
@@ -912,60 +924,66 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF404040"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF404040"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -976,7 +994,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1004,88 +1022,64 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1275,23 +1269,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.25"/>
-    <col customWidth="1" min="2" max="2" width="46.38"/>
-    <col customWidth="1" min="3" max="3" width="69.75"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" customWidth="1"/>
+    <col min="3" max="3" width="69.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +1299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1313,7 +1310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1324,7 +1321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1335,7 +1332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1346,7 +1343,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1357,7 +1354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -1368,7 +1365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1379,7 +1376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1390,23 +1387,25 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1417,7 +1416,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
@@ -1428,7 +1427,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -1439,7 +1438,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
@@ -1461,7 +1460,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
@@ -1472,23 +1471,25 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
@@ -1499,7 +1500,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
@@ -1510,7 +1511,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>53</v>
       </c>
@@ -1526,367 +1527,369 @@
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A20:C20"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.38"/>
-    <col customWidth="1" min="2" max="2" width="82.38"/>
-    <col customWidth="1" min="3" max="3" width="64.0"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="82.42578125" customWidth="1"/>
+    <col min="3" max="3" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="s">
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="s">
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="s">
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="7"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="7"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="7"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D26" s="7"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+      <c r="D27" s="6"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="15" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>137</v>
       </c>
@@ -1897,7 +1900,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>140</v>
       </c>
@@ -1908,7 +1911,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>143</v>
       </c>
@@ -1919,7 +1922,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>146</v>
       </c>
@@ -1930,7 +1933,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>149</v>
       </c>
@@ -1941,7 +1944,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>152</v>
       </c>
@@ -1952,7 +1955,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>155</v>
       </c>
@@ -1967,26 +1970,26 @@
   <mergeCells count="1">
     <mergeCell ref="A29:C29"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="53.75"/>
-    <col customWidth="1" min="2" max="2" width="17.13"/>
+    <col min="1" max="1" width="53.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>158</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1996,8 +1999,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>161</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2007,8 +2010,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
         <v>164</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -2018,8 +2021,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>167</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -2029,7 +2032,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>170</v>
       </c>
@@ -2037,192 +2040,195 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>172</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.5"/>
-    <col customWidth="1" min="2" max="2" width="81.13"/>
-    <col customWidth="1" min="3" max="3" width="60.13"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="81.140625" customWidth="1"/>
+    <col min="3" max="3" width="60.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="12"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="s">
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="12"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="s">
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="s">
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="s">
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D8" s="12"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="s">
+      <c r="D8" s="11"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="12"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="s">
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="s">
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="s">
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13"/>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="12"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>206</v>
       </c>
@@ -2233,7 +2239,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>208</v>
       </c>
@@ -2244,7 +2250,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>211</v>
       </c>
@@ -2255,7 +2261,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>214</v>
       </c>
@@ -2266,7 +2272,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>216</v>
       </c>
@@ -2277,7 +2283,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>218</v>
       </c>
@@ -2288,7 +2294,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>221</v>
       </c>
@@ -2299,23 +2305,25 @@
         <v>223</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="15" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>225</v>
       </c>
@@ -2326,7 +2334,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>228</v>
       </c>
@@ -2342,164 +2350,166 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A24:C24"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.5"/>
-    <col customWidth="1" min="2" max="2" width="100.0"/>
-    <col customWidth="1" min="3" max="3" width="61.5"/>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="3" max="3" width="61.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="14" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>261</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2509,8 +2519,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>264</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -2520,8 +2530,8 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>266</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2535,6 +2545,6 @@
   <mergeCells count="1">
     <mergeCell ref="A16:C16"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Шпаргалка.xlsx
+++ b/Шпаргалка.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610"/>
   </bookViews>
   <sheets>
     <sheet name="Общие операции" sheetId="1" r:id="rId1"/>
@@ -565,6 +565,8 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t>range(4)</t>
     </r>
@@ -573,6 +575,8 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> - это просто последовательность</t>
     </r>
@@ -587,6 +591,8 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t xml:space="preserve">i </t>
     </r>
@@ -595,6 +601,8 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t xml:space="preserve">- название перменной, в которой хранится 
 каждое значение последовательности. Оно может быть любым. </t>
@@ -937,12 +945,16 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -950,23 +962,31 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -974,18 +994,24 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF404040"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF404040"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1972,7 +1998,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
 </worksheet>
 </file>
 
